--- a/tools/excel/enisa/enisa-sme-cra-maturity.xlsx
+++ b/tools/excel/enisa/enisa-sme-cra-maturity.xlsx
@@ -1245,7 +1245,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Are vulnerabilities and updates prioritized based on risk, potential impact?</t>
+          <t>Are vulnerabilities and updates prioritised based on risk and potential impact?</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
